--- a/tools/cfgtool/xls/task.xlsx
+++ b/tools/cfgtool/xls/task.xlsx
@@ -8,9 +8,8 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkCode\tools\bf_xlsx_tool\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D0726A-42FD-4E4E-9B42-63D923EFCD24}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14175"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="10" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>TaskID</t>
   </si>
@@ -138,74 +137,80 @@
   <si>
     <t>[]Reward</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001|-12;1002|23;1003|-2</t>
+  </si>
+  <si>
+    <t>道具类型-金币,22,13,20|道具类型-钻石,40,13,20</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -218,7 +223,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,16 +238,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -256,37 +261,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -294,7 +299,7 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -307,7 +312,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
       <a:dk1>
@@ -557,17 +562,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="27.375" style="4" customWidth="1"/>
-    <col min="6" max="7" width="9.75" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" style="4" width="7.25"/>
+    <col customWidth="true" max="2" min="2" style="4" width="28"/>
+    <col customWidth="true" max="3" min="3" style="4" width="9.75"/>
+    <col customWidth="true" max="4" min="4" style="4" width="6.5"/>
+    <col customWidth="true" max="5" min="5" style="4" width="27.375"/>
+    <col customWidth="true" max="7" min="6" width="9.75"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7">
       <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
@@ -586,7 +591,7 @@
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -605,7 +610,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -624,7 +629,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7">
       <c r="A4" s="10" t="s">
         <v>26</v>
       </c>
@@ -643,12 +648,12 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>24</v>
@@ -657,13 +662,13 @@
         <v>10</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
